--- a/artfynd/A 60375-2025 artfynd.xlsx
+++ b/artfynd/A 60375-2025 artfynd.xlsx
@@ -21963,7 +21963,7 @@
         <v>124455015</v>
       </c>
       <c r="B183" t="n">
-        <v>57658</v>
+        <v>57684</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>

--- a/artfynd/A 60375-2025 artfynd.xlsx
+++ b/artfynd/A 60375-2025 artfynd.xlsx
@@ -22069,7 +22069,7 @@
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>

--- a/artfynd/A 60375-2025 artfynd.xlsx
+++ b/artfynd/A 60375-2025 artfynd.xlsx
@@ -21963,7 +21963,7 @@
         <v>124455015</v>
       </c>
       <c r="B183" t="n">
-        <v>57684</v>
+        <v>57686</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>

--- a/artfynd/A 60375-2025 artfynd.xlsx
+++ b/artfynd/A 60375-2025 artfynd.xlsx
@@ -22069,7 +22069,7 @@
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>

--- a/artfynd/A 60375-2025 artfynd.xlsx
+++ b/artfynd/A 60375-2025 artfynd.xlsx
@@ -21963,7 +21963,7 @@
         <v>124455015</v>
       </c>
       <c r="B183" t="n">
-        <v>57686</v>
+        <v>57694</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>

--- a/artfynd/A 60375-2025 artfynd.xlsx
+++ b/artfynd/A 60375-2025 artfynd.xlsx
@@ -21963,7 +21963,7 @@
         <v>124455015</v>
       </c>
       <c r="B183" t="n">
-        <v>57694</v>
+        <v>57695</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>

--- a/artfynd/A 60375-2025 artfynd.xlsx
+++ b/artfynd/A 60375-2025 artfynd.xlsx
@@ -21963,7 +21963,7 @@
         <v>124455015</v>
       </c>
       <c r="B183" t="n">
-        <v>57695</v>
+        <v>57696</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>

--- a/artfynd/A 60375-2025 artfynd.xlsx
+++ b/artfynd/A 60375-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY192"/>
+  <dimension ref="A1:AZ192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124453534</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124454602</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124457612</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124451344</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124464044</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,6 +1374,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124464713</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1456,6 +1491,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124449603</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1568,6 +1608,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124451578</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1680,6 +1725,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124453554</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1792,6 +1842,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124455518</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1904,6 +1959,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124458497</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2016,6 +2076,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124459079</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2128,6 +2193,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124459169</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2240,6 +2310,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124459560</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2352,6 +2427,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124451649</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2464,6 +2544,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124452995</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2576,6 +2661,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124459246</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2688,6 +2778,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124459530</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2823,6 +2918,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124458477</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2935,6 +3035,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124452233</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3047,6 +3152,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124456762</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3159,6 +3269,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124458130</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3271,6 +3386,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124458517</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3383,6 +3503,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124465552</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3495,6 +3620,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124447955</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3612,6 +3742,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131927222</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3724,6 +3859,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124447789</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3836,6 +3976,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124452814</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3948,6 +4093,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124454121</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4060,6 +4210,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124457379</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4172,6 +4327,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124451835</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4284,6 +4444,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124447061</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4396,6 +4561,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124447135</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4508,6 +4678,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124448916</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4629,6 +4804,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124449149</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4741,6 +4921,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124451374</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4853,6 +5038,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124452779</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4965,6 +5155,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124453753</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5077,6 +5272,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124454161</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5189,6 +5389,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124454594</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5301,6 +5506,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124454678</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5413,6 +5623,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124454800</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5525,6 +5740,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124457291</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5646,6 +5866,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124457982</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5758,6 +5983,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124458121</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5870,6 +6100,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124458954</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5991,6 +6226,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124459788</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6103,6 +6343,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124460214</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6215,6 +6460,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124460549</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6327,6 +6577,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124463101</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6439,6 +6694,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124464465</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6551,6 +6811,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124464656</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6663,6 +6928,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124465031</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6775,6 +7045,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124465301</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6887,6 +7162,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124466116</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7008,6 +7288,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124466958</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7120,6 +7405,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124467315</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7232,6 +7522,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124447712</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7344,6 +7639,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124464120</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7456,6 +7756,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124457780</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7568,6 +7873,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124447566</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7680,6 +7990,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124447843</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7792,6 +8107,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124448067</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7904,6 +8224,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124451806</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8016,6 +8341,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124451894</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8128,6 +8458,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124452223</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8240,6 +8575,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124452903</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8352,6 +8692,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124453195</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8464,6 +8809,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124453342</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8576,6 +8926,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124453984</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8688,6 +9043,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124454282</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8800,6 +9160,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124455021</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8912,6 +9277,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124458002</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9024,6 +9394,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124459044</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9136,6 +9511,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124459186</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9248,6 +9628,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124462400</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9360,6 +9745,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124464738</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9472,6 +9862,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124464945</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9584,6 +9979,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124465980</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9696,6 +10096,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124466463</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9808,6 +10213,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124463334</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9920,6 +10330,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124461083</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10032,6 +10447,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124461212</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10144,6 +10564,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124462439</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10256,6 +10681,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124462570</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10368,6 +10798,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124462686</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10480,6 +10915,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124462929</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10592,6 +11032,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124463308</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10704,6 +11149,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124464053</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10816,6 +11266,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124459871</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10928,6 +11383,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124452111</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11040,6 +11500,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124451942</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11152,6 +11617,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124452252</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11264,6 +11734,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124456604</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11376,6 +11851,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124457577</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11488,6 +11968,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124458985</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11600,6 +12085,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124463850</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11712,6 +12202,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124465334</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11824,6 +12319,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124452524</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11936,6 +12436,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124456913</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12048,6 +12553,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124454557</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12169,6 +12679,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124460160</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12281,6 +12796,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124447855</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12393,6 +12913,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124450959</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12505,6 +13030,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124452335</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12617,6 +13147,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124455107</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12729,6 +13264,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124455549</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12841,6 +13381,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124456825</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12953,6 +13498,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124458601</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13065,6 +13615,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124459017</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13177,6 +13732,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124459961</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13289,6 +13849,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124465683</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13401,6 +13966,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124467045</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13513,6 +14083,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124452305</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13625,6 +14200,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124454771</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13737,6 +14317,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124456787</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13849,6 +14434,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124464357</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13961,6 +14551,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124450918</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14073,6 +14668,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124452019</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14185,6 +14785,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124454920</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14297,6 +14902,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124458998</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14409,6 +15019,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124459298</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14526,6 +15141,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124459477</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14643,6 +15263,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124464583</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14760,6 +15385,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124447394</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14877,6 +15507,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124448100</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14994,6 +15629,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124449557</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15111,6 +15751,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124455432</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15228,6 +15873,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124455697</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15345,6 +15995,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124456467</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15487,6 +16142,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131925541</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15632,6 +16292,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131926004</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15777,6 +16442,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131926058</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15922,6 +16592,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131926082</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -16067,6 +16742,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131926147</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -16212,6 +16892,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131926204</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16333,6 +17018,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124450863</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16445,6 +17135,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124458734</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16561,6 +17256,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124455015</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16682,6 +17382,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124456509</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16808,6 +17513,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124450168</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16929,6 +17639,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124461976</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -17046,6 +17761,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131926501</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -17153,6 +17873,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124465641</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -17279,6 +18004,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124455106</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -17391,6 +18121,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124459297</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17503,6 +18238,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124454537</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17610,6 +18350,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124452642</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17717,6 +18462,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124453365</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17829,6 +18579,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124456983</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17936,6 +18691,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124457172</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -18048,6 +18808,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124447872</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -18160,6 +18925,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124447967</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -18272,6 +19042,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124448755</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -18384,6 +19159,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124448758</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -18496,6 +19276,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124449191</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18603,6 +19388,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124449387</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18715,6 +19505,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124449498</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18827,6 +19622,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124452176</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18939,6 +19739,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124452541</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -19051,6 +19856,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124452969</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -19163,6 +19973,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124453283</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -19275,6 +20090,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124453641</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -19387,6 +20207,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124453757</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -19499,6 +20324,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124454221</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -19611,6 +20441,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124454733</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19723,6 +20558,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124457081</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19835,6 +20675,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124457471</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19947,6 +20792,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124457773</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -20059,6 +20909,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124459487</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -20171,6 +21026,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124459858</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -20283,6 +21143,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124460183</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -20395,6 +21260,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124460812</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -20507,6 +21377,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124464264</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -20619,6 +21494,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124464548</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -20731,6 +21611,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124465595</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -20843,6 +21728,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124466599</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20955,6 +21845,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124462884</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -21067,6 +21962,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124463287</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -21179,6 +22079,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124463955</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -21291,6 +22196,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124464212</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -21403,6 +22313,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124453869</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -21515,6 +22430,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124452003</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -21627,6 +22547,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124456799</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -21739,6 +22664,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124457598</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -21851,6 +22781,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124463372</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -21963,6 +22898,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124464297</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -22075,6 +23015,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124447866</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -22197,6 +23142,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124454879</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -22319,6 +23269,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124465581</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -22441,8 +23396,206 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124452502</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>